--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Nacimiento</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Contulmo</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:17</t>
+    <t xml:space="preserve">2026-10-04 08:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:46</t>
+    <t xml:space="preserve">2026-10-05 09:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -784,7 +784,7 @@
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>652461.12</v>
+        <v>652461.13</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +801,7 @@
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>644468.62</v>
+        <v>644468.63</v>
       </c>
     </row>
     <row r="16">
@@ -886,7 +886,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>608599.12</v>
+        <v>608599.13</v>
       </c>
     </row>
     <row r="21">
@@ -1039,7 +1039,7 @@
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>563989.12</v>
+        <v>563989.13</v>
       </c>
     </row>
     <row r="30">
